--- a/histograms/histogram_frac_s_valence_electrons.xlsx
+++ b/histograms/histogram_frac_s_valence_electrons.xlsx
@@ -445,7 +445,7 @@
         <v>0.15075</v>
       </c>
       <c r="B2" t="n">
-        <v>286</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>0.17225</v>
       </c>
       <c r="B3" t="n">
-        <v>1155</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>0.19375</v>
       </c>
       <c r="B4" t="n">
-        <v>862</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>0.21525</v>
       </c>
       <c r="B5" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>0.23675</v>
       </c>
       <c r="B6" t="n">
-        <v>440</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>0.25825</v>
       </c>
       <c r="B7" t="n">
-        <v>994</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>0.2797500000000001</v>
       </c>
       <c r="B8" t="n">
-        <v>476</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>0.30125</v>
       </c>
       <c r="B9" t="n">
-        <v>324</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>0.32275</v>
       </c>
       <c r="B10" t="n">
-        <v>1265</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>0.3442500000000001</v>
       </c>
       <c r="B11" t="n">
-        <v>4840</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>0.36575</v>
       </c>
       <c r="B12" t="n">
-        <v>3652</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>0.38725</v>
       </c>
       <c r="B13" t="n">
-        <v>1641</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>0.4087500000000001</v>
       </c>
       <c r="B14" t="n">
-        <v>4005</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>0.43025</v>
       </c>
       <c r="B15" t="n">
-        <v>247</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>0.45175</v>
       </c>
       <c r="B16" t="n">
-        <v>1108</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>0.4732500000000001</v>
       </c>
       <c r="B17" t="n">
-        <v>470</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>0.49475</v>
       </c>
       <c r="B18" t="n">
-        <v>1631</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>0.5162500000000001</v>
       </c>
       <c r="B19" t="n">
-        <v>1350</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>0.53775</v>
       </c>
       <c r="B20" t="n">
-        <v>988</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>0.55925</v>
       </c>
       <c r="B21" t="n">
-        <v>627</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
